--- a/seguimiento.xlsx
+++ b/seguimiento.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jugadores" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mediciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criterios pliegues" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -113,6 +114,14 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -658,6 +667,20 @@
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Los datos precargados salen de las planillas de cada categoría. 2013: febrero y junio 2026 (sin fecha de medición todavía) y octubre 2026 (con fechas de nacimiento). 2014: febrero y junio 2026, sin fechas todavía. 2015: febrero, junio y octubre 2026. 2016: febrero, junio y septiembre 2026. La categoría 2014 no tenía talla de enero/febrero. Los dos "Thiago Gonzalez" (2014 y 2015) llevan la categoría entre paréntesis para que el portal no los mezcle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Pliegues: en "Mediciones" la columna "Pliegues Σ6 (mm)" lleva la suma de los 6 pliegues de esa medición (vacía si no se midió; no poner 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Los cortes de zona de cada categoría se cambian en la hoja "Criterios pliegues".</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F383"/>
+  <dimension ref="A1:G383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3047,6 +3070,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3080,6 +3104,11 @@
           <t>Observaciones</t>
         </is>
       </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Pliegues Σ6 (mm)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -3102,6 +3131,9 @@
         <v>150</v>
       </c>
       <c r="F2" s="7" t="n"/>
+      <c r="G2" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -3124,6 +3156,9 @@
         <v>162</v>
       </c>
       <c r="F3" s="7" t="n"/>
+      <c r="G3" s="13" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -3146,6 +3181,9 @@
         <v>144</v>
       </c>
       <c r="F4" s="7" t="n"/>
+      <c r="G4" s="13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -3168,6 +3206,9 @@
         <v>153</v>
       </c>
       <c r="F5" s="7" t="n"/>
+      <c r="G5" s="13" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3190,6 +3231,9 @@
         <v>172</v>
       </c>
       <c r="F6" s="7" t="n"/>
+      <c r="G6" s="13" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3212,6 +3256,9 @@
         <v>163</v>
       </c>
       <c r="F7" s="7" t="n"/>
+      <c r="G7" s="13" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3234,6 +3281,9 @@
         <v>165</v>
       </c>
       <c r="F8" s="7" t="n"/>
+      <c r="G8" s="13" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -3256,6 +3306,9 @@
         <v>159</v>
       </c>
       <c r="F9" s="7" t="n"/>
+      <c r="G9" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -3278,6 +3331,9 @@
         <v>155</v>
       </c>
       <c r="F10" s="7" t="n"/>
+      <c r="G10" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3300,6 +3356,9 @@
         <v>167</v>
       </c>
       <c r="F11" s="7" t="n"/>
+      <c r="G11" s="13" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3322,6 +3381,9 @@
         <v>156</v>
       </c>
       <c r="F12" s="7" t="n"/>
+      <c r="G12" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3344,6 +3406,9 @@
         <v>149</v>
       </c>
       <c r="F13" s="7" t="n"/>
+      <c r="G13" s="13" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3366,6 +3431,9 @@
         <v>164</v>
       </c>
       <c r="F14" s="7" t="n"/>
+      <c r="G14" s="13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -3388,6 +3456,9 @@
         <v>168</v>
       </c>
       <c r="F15" s="7" t="n"/>
+      <c r="G15" s="13" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -3410,6 +3481,9 @@
         <v>151</v>
       </c>
       <c r="F16" s="7" t="n"/>
+      <c r="G16" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -3432,6 +3506,9 @@
         <v>149</v>
       </c>
       <c r="F17" s="7" t="n"/>
+      <c r="G17" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -3454,6 +3531,9 @@
         <v>141</v>
       </c>
       <c r="F18" s="7" t="n"/>
+      <c r="G18" s="13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -3476,6 +3556,9 @@
         <v>149</v>
       </c>
       <c r="F19" s="7" t="n"/>
+      <c r="G19" s="13" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -3498,6 +3581,9 @@
         <v>161</v>
       </c>
       <c r="F20" s="7" t="n"/>
+      <c r="G20" s="13" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -3520,6 +3606,9 @@
         <v>141</v>
       </c>
       <c r="F21" s="7" t="n"/>
+      <c r="G21" s="13" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3542,6 +3631,9 @@
         <v>143</v>
       </c>
       <c r="F22" s="7" t="n"/>
+      <c r="G22" s="13" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -3564,6 +3656,9 @@
         <v>145</v>
       </c>
       <c r="F23" s="7" t="n"/>
+      <c r="G23" s="13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -3586,6 +3681,9 @@
         <v>170</v>
       </c>
       <c r="F24" s="7" t="n"/>
+      <c r="G24" s="13" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -3608,6 +3706,9 @@
         <v>154</v>
       </c>
       <c r="F25" s="7" t="n"/>
+      <c r="G25" s="13" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -3630,6 +3731,9 @@
         <v>161</v>
       </c>
       <c r="F26" s="7" t="n"/>
+      <c r="G26" s="13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3652,6 +3756,9 @@
         <v>157</v>
       </c>
       <c r="F27" s="7" t="n"/>
+      <c r="G27" s="13" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -3674,6 +3781,9 @@
         <v>150</v>
       </c>
       <c r="F28" s="7" t="n"/>
+      <c r="G28" s="13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3696,6 +3806,9 @@
         <v>155</v>
       </c>
       <c r="F29" s="7" t="n"/>
+      <c r="G29" s="13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3718,6 +3831,9 @@
         <v>152</v>
       </c>
       <c r="F30" s="7" t="n"/>
+      <c r="G30" s="13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -3740,6 +3856,9 @@
         <v>170</v>
       </c>
       <c r="F31" s="7" t="n"/>
+      <c r="G31" s="13" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3762,6 +3881,9 @@
         <v>153</v>
       </c>
       <c r="F32" s="7" t="n"/>
+      <c r="G32" s="13" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3784,6 +3906,9 @@
         <v>162</v>
       </c>
       <c r="F33" s="7" t="n"/>
+      <c r="G33" s="13" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -3802,6 +3927,9 @@
       </c>
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="7" t="n"/>
+      <c r="G34" s="13" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -3820,6 +3948,9 @@
       </c>
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="7" t="n"/>
+      <c r="G35" s="13" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -3838,6 +3969,9 @@
       </c>
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="7" t="n"/>
+      <c r="G36" s="13" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -3856,6 +3990,9 @@
       </c>
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="7" t="n"/>
+      <c r="G37" s="13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -3874,6 +4011,9 @@
       </c>
       <c r="E38" s="11" t="n"/>
       <c r="F38" s="7" t="n"/>
+      <c r="G38" s="13" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -3892,6 +4032,9 @@
       </c>
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="7" t="n"/>
+      <c r="G39" s="13" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -3910,6 +4053,9 @@
       </c>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="7" t="n"/>
+      <c r="G40" s="13" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -3928,6 +4074,9 @@
       </c>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="7" t="n"/>
+      <c r="G41" s="13" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -3946,6 +4095,9 @@
       </c>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="7" t="n"/>
+      <c r="G42" s="13" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -3964,6 +4116,9 @@
       </c>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="7" t="n"/>
+      <c r="G43" s="13" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -3982,6 +4137,9 @@
       </c>
       <c r="E44" s="11" t="n"/>
       <c r="F44" s="7" t="n"/>
+      <c r="G44" s="13" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -4000,6 +4158,9 @@
       </c>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="7" t="n"/>
+      <c r="G45" s="13" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -4018,6 +4179,9 @@
       </c>
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="7" t="n"/>
+      <c r="G46" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -4036,6 +4200,9 @@
       </c>
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="7" t="n"/>
+      <c r="G47" s="13" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -4054,6 +4221,9 @@
       </c>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="7" t="n"/>
+      <c r="G48" s="13" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -4072,6 +4242,9 @@
       </c>
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="7" t="n"/>
+      <c r="G49" s="13" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -4090,6 +4263,9 @@
       </c>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="7" t="n"/>
+      <c r="G50" s="13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -4108,6 +4284,9 @@
       </c>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="7" t="n"/>
+      <c r="G51" s="13" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -4126,6 +4305,9 @@
       </c>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="7" t="n"/>
+      <c r="G52" s="13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -4144,6 +4326,9 @@
       </c>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="7" t="n"/>
+      <c r="G53" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -4162,6 +4347,9 @@
       </c>
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="7" t="n"/>
+      <c r="G54" s="13" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -4180,6 +4368,9 @@
       </c>
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="7" t="n"/>
+      <c r="G55" s="13" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -4198,6 +4389,9 @@
       </c>
       <c r="E56" s="11" t="n"/>
       <c r="F56" s="7" t="n"/>
+      <c r="G56" s="13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -4216,6 +4410,9 @@
       </c>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="7" t="n"/>
+      <c r="G57" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -4234,6 +4431,9 @@
       </c>
       <c r="E58" s="11" t="n"/>
       <c r="F58" s="7" t="n"/>
+      <c r="G58" s="13" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -4252,6 +4452,9 @@
       </c>
       <c r="E59" s="11" t="n"/>
       <c r="F59" s="7" t="n"/>
+      <c r="G59" s="13" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -4270,6 +4473,9 @@
       </c>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="7" t="n"/>
+      <c r="G60" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -4288,6 +4494,9 @@
       </c>
       <c r="E61" s="11" t="n"/>
       <c r="F61" s="7" t="n"/>
+      <c r="G61" s="13" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -4306,6 +4515,9 @@
       </c>
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="7" t="n"/>
+      <c r="G62" s="13" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -4324,6 +4536,9 @@
       </c>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="7" t="n"/>
+      <c r="G63" s="13" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -4342,6 +4557,9 @@
       </c>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="7" t="n"/>
+      <c r="G64" s="13" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -4360,6 +4578,9 @@
       </c>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="7" t="n"/>
+      <c r="G65" s="13" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -4378,6 +4599,9 @@
       </c>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="7" t="n"/>
+      <c r="G66" s="13" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -4396,6 +4620,9 @@
       </c>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="7" t="n"/>
+      <c r="G67" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -4418,6 +4645,9 @@
         <v>149.5</v>
       </c>
       <c r="F68" s="7" t="n"/>
+      <c r="G68" s="13" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -4440,6 +4670,9 @@
         <v>164</v>
       </c>
       <c r="F69" s="7" t="n"/>
+      <c r="G69" s="13" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -4462,6 +4695,9 @@
         <v>144</v>
       </c>
       <c r="F70" s="7" t="n"/>
+      <c r="G70" s="13" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -4488,6 +4724,9 @@
           <t>Revisar talla: +6 cm entre febrero (153) y junio (159)</t>
         </is>
       </c>
+      <c r="G71" s="13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -4510,6 +4749,9 @@
         <v>174</v>
       </c>
       <c r="F72" s="7" t="n"/>
+      <c r="G72" s="13" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -4532,6 +4774,9 @@
         <v>165</v>
       </c>
       <c r="F73" s="7" t="n"/>
+      <c r="G73" s="13" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -4554,6 +4799,9 @@
         <v>169</v>
       </c>
       <c r="F74" s="7" t="n"/>
+      <c r="G74" s="13" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -4576,6 +4824,9 @@
         <v>159</v>
       </c>
       <c r="F75" s="7" t="n"/>
+      <c r="G75" s="13" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -4598,6 +4849,9 @@
         <v>157</v>
       </c>
       <c r="F76" s="7" t="n"/>
+      <c r="G76" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -4620,6 +4874,9 @@
         <v>170</v>
       </c>
       <c r="F77" s="7" t="n"/>
+      <c r="G77" s="13" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -4642,6 +4899,9 @@
         <v>159</v>
       </c>
       <c r="F78" s="7" t="n"/>
+      <c r="G78" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -4664,6 +4924,9 @@
         <v>151</v>
       </c>
       <c r="F79" s="7" t="n"/>
+      <c r="G79" s="13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -4690,6 +4953,9 @@
           <t>Revisar talla: +6 cm entre febrero (164) y junio (170)</t>
         </is>
       </c>
+      <c r="G80" s="13" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -4712,6 +4978,9 @@
         <v>171</v>
       </c>
       <c r="F81" s="7" t="n"/>
+      <c r="G81" s="13" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -4734,6 +5003,9 @@
         <v>151</v>
       </c>
       <c r="F82" s="7" t="n"/>
+      <c r="G82" s="13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -4756,6 +5028,9 @@
         <v>152</v>
       </c>
       <c r="F83" s="7" t="n"/>
+      <c r="G83" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -4778,6 +5053,7 @@
         <v>144</v>
       </c>
       <c r="F84" s="7" t="n"/>
+      <c r="G84" s="13" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -4800,6 +5076,9 @@
         <v>148</v>
       </c>
       <c r="F85" s="7" t="n"/>
+      <c r="G85" s="13" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -4822,6 +5101,9 @@
         <v>160</v>
       </c>
       <c r="F86" s="7" t="n"/>
+      <c r="G86" s="13" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -4848,6 +5130,9 @@
           <t>Revisar talla: +5 cm entre febrero (141) y junio (146)</t>
         </is>
       </c>
+      <c r="G87" s="13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -4870,6 +5155,9 @@
         <v>147</v>
       </c>
       <c r="F88" s="7" t="n"/>
+      <c r="G88" s="13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -4892,6 +5180,9 @@
         <v>146</v>
       </c>
       <c r="F89" s="7" t="n"/>
+      <c r="G89" s="13" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -4914,6 +5205,9 @@
         <v>172</v>
       </c>
       <c r="F90" s="7" t="n"/>
+      <c r="G90" s="13" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -4936,6 +5230,9 @@
         <v>154</v>
       </c>
       <c r="F91" s="7" t="n"/>
+      <c r="G91" s="13" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -4958,6 +5255,9 @@
         <v>163</v>
       </c>
       <c r="F92" s="7" t="n"/>
+      <c r="G92" s="13" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -4980,6 +5280,9 @@
         <v>160</v>
       </c>
       <c r="F93" s="7" t="n"/>
+      <c r="G93" s="13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -5002,6 +5305,9 @@
         <v>153</v>
       </c>
       <c r="F94" s="7" t="n"/>
+      <c r="G94" s="13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -5028,6 +5334,9 @@
           <t>Revisar: +6 cm de talla (155 → 161) y +6,1 kg de peso (43,4 → 49,5) entre febrero y junio</t>
         </is>
       </c>
+      <c r="G95" s="13" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -5054,6 +5363,9 @@
           <t>Revisar talla: +5 cm entre febrero (152) y junio (157)</t>
         </is>
       </c>
+      <c r="G96" s="13" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -5076,6 +5388,9 @@
         <v>170.5</v>
       </c>
       <c r="F97" s="7" t="n"/>
+      <c r="G97" s="13" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -5098,6 +5413,9 @@
         <v>152</v>
       </c>
       <c r="F98" s="7" t="n"/>
+      <c r="G98" s="13" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -5120,6 +5438,9 @@
         <v>165</v>
       </c>
       <c r="F99" s="7" t="n"/>
+      <c r="G99" s="13" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -5142,6 +5463,9 @@
         <v>166</v>
       </c>
       <c r="F100" s="7" t="n"/>
+      <c r="G100" s="13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -5164,6 +5488,9 @@
         <v>153</v>
       </c>
       <c r="F101" s="7" t="n"/>
+      <c r="G101" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -5186,6 +5513,9 @@
         <v>145</v>
       </c>
       <c r="F102" s="7" t="n"/>
+      <c r="G102" s="13" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -5208,6 +5538,9 @@
         <v>153</v>
       </c>
       <c r="F103" s="7" t="n"/>
+      <c r="G103" s="13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -5230,6 +5563,9 @@
         <v>177</v>
       </c>
       <c r="F104" s="7" t="n"/>
+      <c r="G104" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -5252,6 +5588,9 @@
         <v>172</v>
       </c>
       <c r="F105" s="7" t="n"/>
+      <c r="G105" s="13" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -5274,6 +5613,9 @@
         <v>171</v>
       </c>
       <c r="F106" s="7" t="n"/>
+      <c r="G106" s="13" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -5296,6 +5638,9 @@
         <v>163</v>
       </c>
       <c r="F107" s="7" t="n"/>
+      <c r="G107" s="13" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
@@ -5316,6 +5661,9 @@
         <v>152</v>
       </c>
       <c r="F108" s="7" t="n"/>
+      <c r="G108" s="13" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
@@ -5336,6 +5684,9 @@
         <v>143</v>
       </c>
       <c r="F109" s="7" t="n"/>
+      <c r="G109" s="13" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
@@ -5356,6 +5707,9 @@
         <v>152</v>
       </c>
       <c r="F110" s="7" t="n"/>
+      <c r="G110" s="13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
@@ -5376,6 +5730,9 @@
         <v>147</v>
       </c>
       <c r="F111" s="7" t="n"/>
+      <c r="G111" s="13" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -5396,6 +5753,9 @@
         <v>156</v>
       </c>
       <c r="F112" s="7" t="n"/>
+      <c r="G112" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -5416,6 +5776,9 @@
         <v>168</v>
       </c>
       <c r="F113" s="7" t="n"/>
+      <c r="G113" s="13" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
@@ -5436,6 +5799,9 @@
         <v>141</v>
       </c>
       <c r="F114" s="7" t="n"/>
+      <c r="G114" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
@@ -5456,6 +5822,9 @@
         <v>145</v>
       </c>
       <c r="F115" s="7" t="n"/>
+      <c r="G115" s="13" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
@@ -5476,6 +5845,9 @@
         <v>138</v>
       </c>
       <c r="F116" s="7" t="n"/>
+      <c r="G116" s="13" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
@@ -5496,6 +5868,9 @@
         <v>149</v>
       </c>
       <c r="F117" s="7" t="n"/>
+      <c r="G117" s="13" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -5516,6 +5891,9 @@
         <v>153</v>
       </c>
       <c r="F118" s="7" t="n"/>
+      <c r="G118" s="13" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -5536,6 +5914,9 @@
         <v>151</v>
       </c>
       <c r="F119" s="7" t="n"/>
+      <c r="G119" s="13" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -5556,6 +5937,9 @@
         <v>163</v>
       </c>
       <c r="F120" s="7" t="n"/>
+      <c r="G120" s="13" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
@@ -5576,6 +5960,9 @@
         <v>160</v>
       </c>
       <c r="F121" s="7" t="n"/>
+      <c r="G121" s="13" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
@@ -5596,6 +5983,9 @@
         <v>140</v>
       </c>
       <c r="F122" s="7" t="n"/>
+      <c r="G122" s="13" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
@@ -5616,6 +6006,9 @@
         <v>148</v>
       </c>
       <c r="F123" s="7" t="n"/>
+      <c r="G123" s="13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
@@ -5636,6 +6029,9 @@
         <v>150</v>
       </c>
       <c r="F124" s="7" t="n"/>
+      <c r="G124" s="13" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
@@ -5656,6 +6052,9 @@
         <v>148</v>
       </c>
       <c r="F125" s="7" t="n"/>
+      <c r="G125" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -5676,6 +6075,9 @@
         <v>154</v>
       </c>
       <c r="F126" s="7" t="n"/>
+      <c r="G126" s="13" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -5696,6 +6098,9 @@
         <v>152</v>
       </c>
       <c r="F127" s="7" t="n"/>
+      <c r="G127" s="13" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
@@ -5716,6 +6121,9 @@
         <v>140</v>
       </c>
       <c r="F128" s="7" t="n"/>
+      <c r="G128" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
@@ -5736,6 +6144,9 @@
         <v>155</v>
       </c>
       <c r="F129" s="7" t="n"/>
+      <c r="G129" s="13" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
@@ -5756,6 +6167,9 @@
         <v>167</v>
       </c>
       <c r="F130" s="7" t="n"/>
+      <c r="G130" s="13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
@@ -5776,6 +6190,9 @@
         <v>161</v>
       </c>
       <c r="F131" s="7" t="n"/>
+      <c r="G131" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
@@ -5796,6 +6213,9 @@
         <v>157</v>
       </c>
       <c r="F132" s="7" t="n"/>
+      <c r="G132" s="13" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -5816,6 +6236,9 @@
         <v>149</v>
       </c>
       <c r="F133" s="7" t="n"/>
+      <c r="G133" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -5836,6 +6259,9 @@
         <v>150</v>
       </c>
       <c r="F134" s="7" t="n"/>
+      <c r="G134" s="13" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
@@ -5856,6 +6282,9 @@
         <v>149</v>
       </c>
       <c r="F135" s="7" t="n"/>
+      <c r="G135" s="13" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
@@ -5876,6 +6305,9 @@
         <v>161</v>
       </c>
       <c r="F136" s="7" t="n"/>
+      <c r="G136" s="13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
@@ -5896,6 +6328,9 @@
         <v>158</v>
       </c>
       <c r="F137" s="7" t="n"/>
+      <c r="G137" s="13" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
@@ -5916,6 +6351,9 @@
         <v>159</v>
       </c>
       <c r="F138" s="7" t="n"/>
+      <c r="G138" s="13" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
@@ -5936,6 +6374,9 @@
         <v>149</v>
       </c>
       <c r="F139" s="7" t="n"/>
+      <c r="G139" s="13" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -5956,6 +6397,9 @@
         <v>149</v>
       </c>
       <c r="F140" s="7" t="n"/>
+      <c r="G140" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -5978,6 +6422,7 @@
         <v>130</v>
       </c>
       <c r="F141" s="7" t="n"/>
+      <c r="G141" s="13" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
@@ -6000,6 +6445,7 @@
         <v>143</v>
       </c>
       <c r="F142" s="7" t="n"/>
+      <c r="G142" s="13" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
@@ -6022,6 +6468,7 @@
         <v>140</v>
       </c>
       <c r="F143" s="7" t="n"/>
+      <c r="G143" s="13" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
@@ -6044,6 +6491,7 @@
         <v>138</v>
       </c>
       <c r="F144" s="7" t="n"/>
+      <c r="G144" s="13" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
@@ -6066,6 +6514,7 @@
         <v>139</v>
       </c>
       <c r="F145" s="7" t="n"/>
+      <c r="G145" s="13" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
@@ -6088,6 +6537,7 @@
         <v>138</v>
       </c>
       <c r="F146" s="7" t="n"/>
+      <c r="G146" s="13" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -6114,6 +6564,7 @@
           <t>Figura como 'Simon Guerrerp' en la planilla (error de tipeo)</t>
         </is>
       </c>
+      <c r="G147" s="13" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -6136,6 +6587,7 @@
         <v>134</v>
       </c>
       <c r="F148" s="7" t="n"/>
+      <c r="G148" s="13" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
@@ -6158,6 +6610,7 @@
         <v>138</v>
       </c>
       <c r="F149" s="7" t="n"/>
+      <c r="G149" s="13" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
@@ -6180,6 +6633,7 @@
         <v>135</v>
       </c>
       <c r="F150" s="7" t="n"/>
+      <c r="G150" s="13" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
@@ -6202,6 +6656,7 @@
         <v>147</v>
       </c>
       <c r="F151" s="7" t="n"/>
+      <c r="G151" s="13" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
@@ -6224,6 +6679,7 @@
         <v>133</v>
       </c>
       <c r="F152" s="7" t="n"/>
+      <c r="G152" s="13" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
@@ -6246,6 +6702,7 @@
         <v>140</v>
       </c>
       <c r="F153" s="7" t="n"/>
+      <c r="G153" s="13" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -6268,6 +6725,7 @@
         <v>139</v>
       </c>
       <c r="F154" s="7" t="n"/>
+      <c r="G154" s="13" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -6290,6 +6748,7 @@
         <v>145</v>
       </c>
       <c r="F155" s="7" t="n"/>
+      <c r="G155" s="13" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
@@ -6312,6 +6771,7 @@
         <v>140</v>
       </c>
       <c r="F156" s="7" t="n"/>
+      <c r="G156" s="13" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
@@ -6334,6 +6794,7 @@
         <v>145</v>
       </c>
       <c r="F157" s="7" t="n"/>
+      <c r="G157" s="13" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
@@ -6358,6 +6819,7 @@
           <t>Peso 30,2 kg excluido: +9,3 kg hasta junio (39,5) y 38,6 en septiembre. A reverificar</t>
         </is>
       </c>
+      <c r="G158" s="13" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
@@ -6380,6 +6842,7 @@
         <v>141</v>
       </c>
       <c r="F159" s="7" t="n"/>
+      <c r="G159" s="13" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
@@ -6402,6 +6865,7 @@
         <v>133</v>
       </c>
       <c r="F160" s="7" t="n"/>
+      <c r="G160" s="13" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -6424,6 +6888,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="n"/>
+      <c r="G161" s="13" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -6446,6 +6911,7 @@
         <v>143</v>
       </c>
       <c r="F162" s="7" t="n"/>
+      <c r="G162" s="13" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
@@ -6468,6 +6934,7 @@
         <v>135</v>
       </c>
       <c r="F163" s="7" t="n"/>
+      <c r="G163" s="13" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
@@ -6494,6 +6961,7 @@
           <t>Figura como 'Dyel Satera' en la planilla de febrero; misma fecha de nacimiento que Thaiel Zattera</t>
         </is>
       </c>
+      <c r="G164" s="13" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
@@ -6516,6 +6984,7 @@
         <v>141.5</v>
       </c>
       <c r="F165" s="7" t="n"/>
+      <c r="G165" s="13" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
@@ -6538,6 +7007,7 @@
         <v>141.5</v>
       </c>
       <c r="F166" s="7" t="n"/>
+      <c r="G166" s="13" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
@@ -6560,6 +7030,7 @@
         <v>140</v>
       </c>
       <c r="F167" s="7" t="n"/>
+      <c r="G167" s="13" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -6582,6 +7053,7 @@
         <v>139.8</v>
       </c>
       <c r="F168" s="7" t="n"/>
+      <c r="G168" s="13" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -6604,6 +7076,7 @@
         <v>133</v>
       </c>
       <c r="F169" s="7" t="n"/>
+      <c r="G169" s="13" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
@@ -6626,6 +7099,7 @@
         <v>131</v>
       </c>
       <c r="F170" s="7" t="n"/>
+      <c r="G170" s="13" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
@@ -6648,6 +7122,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="n"/>
+      <c r="G171" s="13" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
@@ -6670,6 +7145,7 @@
         <v>141</v>
       </c>
       <c r="F172" s="7" t="n"/>
+      <c r="G172" s="13" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
@@ -6692,6 +7168,7 @@
         <v>140.5</v>
       </c>
       <c r="F173" s="7" t="n"/>
+      <c r="G173" s="13" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
@@ -6714,6 +7191,7 @@
         <v>140</v>
       </c>
       <c r="F174" s="7" t="n"/>
+      <c r="G174" s="13" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -6736,6 +7214,7 @@
         <v>139</v>
       </c>
       <c r="F175" s="7" t="n"/>
+      <c r="G175" s="13" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -6758,6 +7237,7 @@
         <v>143</v>
       </c>
       <c r="F176" s="7" t="n"/>
+      <c r="G176" s="13" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
@@ -6780,6 +7260,7 @@
         <v>135</v>
       </c>
       <c r="F177" s="7" t="n"/>
+      <c r="G177" s="13" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
@@ -6802,6 +7283,7 @@
         <v>138</v>
       </c>
       <c r="F178" s="7" t="n"/>
+      <c r="G178" s="13" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
@@ -6824,6 +7306,7 @@
         <v>136</v>
       </c>
       <c r="F179" s="7" t="n"/>
+      <c r="G179" s="13" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
@@ -6846,6 +7329,7 @@
         <v>148</v>
       </c>
       <c r="F180" s="7" t="n"/>
+      <c r="G180" s="13" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
@@ -6868,6 +7352,7 @@
         <v>133.5</v>
       </c>
       <c r="F181" s="7" t="n"/>
+      <c r="G181" s="13" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -6890,6 +7375,7 @@
         <v>141</v>
       </c>
       <c r="F182" s="7" t="n"/>
+      <c r="G182" s="13" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -6912,6 +7398,7 @@
         <v>140</v>
       </c>
       <c r="F183" s="7" t="n"/>
+      <c r="G183" s="13" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
@@ -6938,6 +7425,7 @@
           <t>Revisar talla: 145 cm (feb) → 148 (jun) → 145 (sep); junio o septiembre está mal</t>
         </is>
       </c>
+      <c r="G184" s="13" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
@@ -6960,6 +7448,7 @@
         <v>141</v>
       </c>
       <c r="F185" s="7" t="n"/>
+      <c r="G185" s="13" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
@@ -6982,6 +7471,7 @@
         <v>145.5</v>
       </c>
       <c r="F186" s="7" t="n"/>
+      <c r="G186" s="13" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
@@ -7006,6 +7496,7 @@
           <t>Talla 142 cm excluida: 133 cm en febrero y 134 cm en septiembre. A reverificar</t>
         </is>
       </c>
+      <c r="G187" s="13" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
@@ -7028,6 +7519,7 @@
         <v>142</v>
       </c>
       <c r="F188" s="7" t="n"/>
+      <c r="G188" s="13" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -7050,6 +7542,7 @@
         <v>134</v>
       </c>
       <c r="F189" s="7" t="n"/>
+      <c r="G189" s="13" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -7072,6 +7565,7 @@
         <v>147</v>
       </c>
       <c r="F190" s="7" t="n"/>
+      <c r="G190" s="13" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
@@ -7094,6 +7588,7 @@
         <v>144</v>
       </c>
       <c r="F191" s="7" t="n"/>
+      <c r="G191" s="13" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
@@ -7116,6 +7611,7 @@
         <v>137</v>
       </c>
       <c r="F192" s="7" t="n"/>
+      <c r="G192" s="13" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
@@ -7138,6 +7634,7 @@
         <v>145.5</v>
       </c>
       <c r="F193" s="7" t="n"/>
+      <c r="G193" s="13" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
@@ -7160,6 +7657,7 @@
         <v>143</v>
       </c>
       <c r="F194" s="7" t="n"/>
+      <c r="G194" s="13" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
@@ -7182,6 +7680,7 @@
         <v>141.5</v>
       </c>
       <c r="F195" s="7" t="n"/>
+      <c r="G195" s="13" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -7204,6 +7703,7 @@
         <v>140</v>
       </c>
       <c r="F196" s="7" t="n"/>
+      <c r="G196" s="13" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -7226,6 +7726,7 @@
         <v>140</v>
       </c>
       <c r="F197" s="7" t="n"/>
+      <c r="G197" s="13" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
@@ -7252,6 +7753,7 @@
           <t>Peso corregido: figuraba como 271 kg</t>
         </is>
       </c>
+      <c r="G198" s="13" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
@@ -7274,6 +7776,7 @@
         <v>142</v>
       </c>
       <c r="F199" s="7" t="n"/>
+      <c r="G199" s="13" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
@@ -7296,6 +7799,7 @@
         <v>147</v>
       </c>
       <c r="F200" s="7" t="n"/>
+      <c r="G200" s="13" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
@@ -7318,6 +7822,7 @@
         <v>140</v>
       </c>
       <c r="F201" s="7" t="n"/>
+      <c r="G201" s="13" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
@@ -7340,6 +7845,7 @@
         <v>153</v>
       </c>
       <c r="F202" s="7" t="n"/>
+      <c r="G202" s="13" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -7362,6 +7868,7 @@
         <v>148</v>
       </c>
       <c r="F203" s="7" t="n"/>
+      <c r="G203" s="13" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -7384,6 +7891,7 @@
         <v>139</v>
       </c>
       <c r="F204" s="7" t="n"/>
+      <c r="G204" s="13" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
@@ -7406,6 +7914,7 @@
         <v>130</v>
       </c>
       <c r="F205" s="7" t="n"/>
+      <c r="G205" s="13" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
@@ -7428,6 +7937,7 @@
         <v>145.5</v>
       </c>
       <c r="F206" s="7" t="n"/>
+      <c r="G206" s="13" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
@@ -7450,6 +7960,7 @@
         <v>140</v>
       </c>
       <c r="F207" s="7" t="n"/>
+      <c r="G207" s="13" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
@@ -7472,6 +7983,7 @@
         <v>139</v>
       </c>
       <c r="F208" s="7" t="n"/>
+      <c r="G208" s="13" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
@@ -7494,6 +8006,7 @@
         <v>141</v>
       </c>
       <c r="F209" s="7" t="n"/>
+      <c r="G209" s="13" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -7516,6 +8029,7 @@
         <v>138.5</v>
       </c>
       <c r="F210" s="7" t="n"/>
+      <c r="G210" s="13" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -7538,6 +8052,7 @@
         <v>142.5</v>
       </c>
       <c r="F211" s="7" t="n"/>
+      <c r="G211" s="13" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
@@ -7560,6 +8075,7 @@
         <v>135</v>
       </c>
       <c r="F212" s="7" t="n"/>
+      <c r="G212" s="13" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
@@ -7582,6 +8098,7 @@
         <v>138.5</v>
       </c>
       <c r="F213" s="7" t="n"/>
+      <c r="G213" s="13" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
@@ -7604,6 +8121,7 @@
         <v>135.5</v>
       </c>
       <c r="F214" s="7" t="n"/>
+      <c r="G214" s="13" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
@@ -7626,6 +8144,7 @@
         <v>149</v>
       </c>
       <c r="F215" s="7" t="n"/>
+      <c r="G215" s="13" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
@@ -7648,6 +8167,7 @@
         <v>132</v>
       </c>
       <c r="F216" s="7" t="n"/>
+      <c r="G216" s="13" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -7670,6 +8190,7 @@
         <v>141</v>
       </c>
       <c r="F217" s="7" t="n"/>
+      <c r="G217" s="13" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -7692,6 +8213,7 @@
         <v>139</v>
       </c>
       <c r="F218" s="7" t="n"/>
+      <c r="G218" s="13" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
@@ -7718,6 +8240,7 @@
           <t>Revisar talla: 145 cm (feb) → 148 (jun) → 145 (sep); junio o septiembre está mal</t>
         </is>
       </c>
+      <c r="G219" s="13" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
@@ -7740,6 +8263,7 @@
         <v>140</v>
       </c>
       <c r="F220" s="7" t="n"/>
+      <c r="G220" s="13" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
@@ -7762,6 +8286,7 @@
         <v>134</v>
       </c>
       <c r="F221" s="7" t="n"/>
+      <c r="G221" s="13" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
@@ -7784,6 +8309,7 @@
         <v>141</v>
       </c>
       <c r="F222" s="7" t="n"/>
+      <c r="G222" s="13" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
@@ -7806,6 +8332,7 @@
         <v>149</v>
       </c>
       <c r="F223" s="7" t="n"/>
+      <c r="G223" s="13" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -7828,6 +8355,7 @@
         <v>136</v>
       </c>
       <c r="F224" s="7" t="n"/>
+      <c r="G224" s="13" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -7850,6 +8378,7 @@
         <v>146</v>
       </c>
       <c r="F225" s="7" t="n"/>
+      <c r="G225" s="13" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
@@ -7872,6 +8401,7 @@
         <v>142</v>
       </c>
       <c r="F226" s="7" t="n"/>
+      <c r="G226" s="13" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
@@ -7894,6 +8424,7 @@
         <v>141.5</v>
       </c>
       <c r="F227" s="7" t="n"/>
+      <c r="G227" s="13" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
@@ -7916,6 +8447,7 @@
         <v>140</v>
       </c>
       <c r="F228" s="7" t="n"/>
+      <c r="G228" s="13" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
@@ -7938,6 +8470,7 @@
         <v>131</v>
       </c>
       <c r="F229" s="7" t="n"/>
+      <c r="G229" s="13" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
@@ -7960,6 +8493,7 @@
         <v>142</v>
       </c>
       <c r="F230" s="7" t="n"/>
+      <c r="G230" s="13" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -7982,6 +8516,7 @@
         <v>146</v>
       </c>
       <c r="F231" s="7" t="n"/>
+      <c r="G231" s="13" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -8004,6 +8539,7 @@
         <v>139</v>
       </c>
       <c r="F232" s="7" t="n"/>
+      <c r="G232" s="13" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
@@ -8026,6 +8562,7 @@
         <v>148</v>
       </c>
       <c r="F233" s="7" t="n"/>
+      <c r="G233" s="13" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
@@ -8050,6 +8587,7 @@
           <t>Talla 147,5 cm excluida: +8,5 cm en 3 meses (139 cm en junio). A reverificar</t>
         </is>
       </c>
+      <c r="G234" s="13" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
@@ -8072,6 +8610,7 @@
         <v>125</v>
       </c>
       <c r="F235" s="7" t="n"/>
+      <c r="G235" s="13" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
@@ -8094,6 +8633,7 @@
         <v>139</v>
       </c>
       <c r="F236" s="7" t="n"/>
+      <c r="G236" s="13" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
@@ -8116,6 +8656,7 @@
         <v>156.5</v>
       </c>
       <c r="F237" s="7" t="n"/>
+      <c r="G237" s="13" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -8138,6 +8679,7 @@
         <v>143</v>
       </c>
       <c r="F238" s="7" t="n"/>
+      <c r="G238" s="13" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -8160,6 +8702,7 @@
         <v>157</v>
       </c>
       <c r="F239" s="7" t="n"/>
+      <c r="G239" s="13" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
@@ -8182,6 +8725,7 @@
         <v>145</v>
       </c>
       <c r="F240" s="7" t="n"/>
+      <c r="G240" s="13" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
@@ -8204,6 +8748,7 @@
         <v>151</v>
       </c>
       <c r="F241" s="7" t="n"/>
+      <c r="G241" s="13" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
@@ -8226,6 +8771,7 @@
         <v>145</v>
       </c>
       <c r="F242" s="7" t="n"/>
+      <c r="G242" s="13" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
@@ -8248,6 +8794,7 @@
         <v>145</v>
       </c>
       <c r="F243" s="7" t="n"/>
+      <c r="G243" s="13" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
@@ -8270,6 +8817,7 @@
         <v>141</v>
       </c>
       <c r="F244" s="7" t="n"/>
+      <c r="G244" s="13" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -8292,6 +8840,7 @@
         <v>144</v>
       </c>
       <c r="F245" s="7" t="n"/>
+      <c r="G245" s="13" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -8314,6 +8863,7 @@
         <v>140</v>
       </c>
       <c r="F246" s="7" t="n"/>
+      <c r="G246" s="13" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
@@ -8336,6 +8886,7 @@
         <v>132</v>
       </c>
       <c r="F247" s="7" t="n"/>
+      <c r="G247" s="13" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
@@ -8358,6 +8909,7 @@
         <v>145</v>
       </c>
       <c r="F248" s="7" t="n"/>
+      <c r="G248" s="13" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
@@ -8380,6 +8932,7 @@
         <v>137</v>
       </c>
       <c r="F249" s="7" t="n"/>
+      <c r="G249" s="13" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
@@ -8402,6 +8955,7 @@
         <v>141</v>
       </c>
       <c r="F250" s="7" t="n"/>
+      <c r="G250" s="13" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
@@ -8424,6 +8978,7 @@
         <v>142</v>
       </c>
       <c r="F251" s="7" t="n"/>
+      <c r="G251" s="13" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
@@ -8446,6 +9001,7 @@
         <v>131</v>
       </c>
       <c r="F252" s="7" t="n"/>
+      <c r="G252" s="13" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
@@ -8468,6 +9024,7 @@
         <v>139</v>
       </c>
       <c r="F253" s="7" t="n"/>
+      <c r="G253" s="13" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
@@ -8490,6 +9047,7 @@
         <v>145</v>
       </c>
       <c r="F254" s="7" t="n"/>
+      <c r="G254" s="13" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
@@ -8512,6 +9070,7 @@
         <v>144</v>
       </c>
       <c r="F255" s="7" t="n"/>
+      <c r="G255" s="13" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
@@ -8534,6 +9093,7 @@
         <v>151</v>
       </c>
       <c r="F256" s="7" t="n"/>
+      <c r="G256" s="13" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
@@ -8556,6 +9116,7 @@
         <v>137</v>
       </c>
       <c r="F257" s="7" t="n"/>
+      <c r="G257" s="13" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
@@ -8578,6 +9139,7 @@
         <v>150</v>
       </c>
       <c r="F258" s="7" t="n"/>
+      <c r="G258" s="13" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
@@ -8600,6 +9162,7 @@
         <v>143</v>
       </c>
       <c r="F259" s="7" t="n"/>
+      <c r="G259" s="13" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
@@ -8622,6 +9185,7 @@
         <v>143</v>
       </c>
       <c r="F260" s="7" t="n"/>
+      <c r="G260" s="13" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
@@ -8644,6 +9208,7 @@
         <v>139</v>
       </c>
       <c r="F261" s="7" t="n"/>
+      <c r="G261" s="13" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
@@ -8666,6 +9231,7 @@
         <v>142</v>
       </c>
       <c r="F262" s="7" t="n"/>
+      <c r="G262" s="13" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
@@ -8688,6 +9254,7 @@
         <v>145</v>
       </c>
       <c r="F263" s="7" t="n"/>
+      <c r="G263" s="13" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
@@ -8710,6 +9277,7 @@
         <v>149</v>
       </c>
       <c r="F264" s="7" t="n"/>
+      <c r="G264" s="13" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
@@ -8732,6 +9300,7 @@
         <v>128</v>
       </c>
       <c r="F265" s="7" t="n"/>
+      <c r="G265" s="13" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
@@ -8754,6 +9323,7 @@
         <v>137</v>
       </c>
       <c r="F266" s="7" t="n"/>
+      <c r="G266" s="13" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
@@ -8776,6 +9346,7 @@
         <v>145</v>
       </c>
       <c r="F267" s="7" t="n"/>
+      <c r="G267" s="13" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
@@ -8798,6 +9369,7 @@
         <v>148</v>
       </c>
       <c r="F268" s="7" t="n"/>
+      <c r="G268" s="13" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
@@ -8820,6 +9392,7 @@
         <v>141</v>
       </c>
       <c r="F269" s="7" t="n"/>
+      <c r="G269" s="13" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
@@ -8842,6 +9415,7 @@
         <v>151</v>
       </c>
       <c r="F270" s="7" t="n"/>
+      <c r="G270" s="13" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
@@ -8864,6 +9438,7 @@
         <v>145</v>
       </c>
       <c r="F271" s="7" t="n"/>
+      <c r="G271" s="13" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
@@ -8886,6 +9461,7 @@
         <v>158</v>
       </c>
       <c r="F272" s="7" t="n"/>
+      <c r="G272" s="13" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
@@ -8908,6 +9484,7 @@
         <v>145</v>
       </c>
       <c r="F273" s="7" t="n"/>
+      <c r="G273" s="13" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
@@ -8934,6 +9511,7 @@
           <t>Talla de junio fijada en 151 cm (figuraba 141)</t>
         </is>
       </c>
+      <c r="G274" s="13" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
@@ -8956,6 +9534,7 @@
         <v>145</v>
       </c>
       <c r="F275" s="7" t="n"/>
+      <c r="G275" s="13" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
@@ -8978,6 +9557,7 @@
         <v>144.5</v>
       </c>
       <c r="F276" s="7" t="n"/>
+      <c r="G276" s="13" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
@@ -9000,6 +9580,7 @@
         <v>140.4</v>
       </c>
       <c r="F277" s="7" t="n"/>
+      <c r="G277" s="13" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
@@ -9022,6 +9603,7 @@
         <v>144</v>
       </c>
       <c r="F278" s="7" t="n"/>
+      <c r="G278" s="13" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
@@ -9044,6 +9626,7 @@
         <v>140</v>
       </c>
       <c r="F279" s="7" t="n"/>
+      <c r="G279" s="13" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
@@ -9066,6 +9649,7 @@
         <v>132</v>
       </c>
       <c r="F280" s="7" t="n"/>
+      <c r="G280" s="13" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
@@ -9088,6 +9672,7 @@
         <v>145</v>
       </c>
       <c r="F281" s="7" t="n"/>
+      <c r="G281" s="13" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="7" t="inlineStr">
@@ -9110,6 +9695,7 @@
         <v>137</v>
       </c>
       <c r="F282" s="7" t="n"/>
+      <c r="G282" s="13" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
@@ -9132,6 +9718,7 @@
         <v>141</v>
       </c>
       <c r="F283" s="7" t="n"/>
+      <c r="G283" s="13" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="inlineStr">
@@ -9154,6 +9741,7 @@
         <v>142</v>
       </c>
       <c r="F284" s="7" t="n"/>
+      <c r="G284" s="13" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
@@ -9176,6 +9764,7 @@
         <v>130.6</v>
       </c>
       <c r="F285" s="7" t="n"/>
+      <c r="G285" s="13" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="7" t="inlineStr">
@@ -9198,6 +9787,7 @@
         <v>138</v>
       </c>
       <c r="F286" s="7" t="n"/>
+      <c r="G286" s="13" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
@@ -9220,6 +9810,7 @@
         <v>145</v>
       </c>
       <c r="F287" s="7" t="n"/>
+      <c r="G287" s="13" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="inlineStr">
@@ -9242,6 +9833,7 @@
         <v>144</v>
       </c>
       <c r="F288" s="7" t="n"/>
+      <c r="G288" s="13" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
@@ -9264,6 +9856,7 @@
         <v>151</v>
       </c>
       <c r="F289" s="7" t="n"/>
+      <c r="G289" s="13" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
@@ -9286,6 +9879,7 @@
         <v>137</v>
       </c>
       <c r="F290" s="7" t="n"/>
+      <c r="G290" s="13" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
@@ -9308,6 +9902,7 @@
         <v>151</v>
       </c>
       <c r="F291" s="7" t="n"/>
+      <c r="G291" s="13" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
@@ -9330,6 +9925,7 @@
         <v>144.5</v>
       </c>
       <c r="F292" s="7" t="n"/>
+      <c r="G292" s="13" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
@@ -9352,6 +9948,7 @@
         <v>142.8</v>
       </c>
       <c r="F293" s="7" t="n"/>
+      <c r="G293" s="13" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
@@ -9374,6 +9971,7 @@
         <v>139</v>
       </c>
       <c r="F294" s="7" t="n"/>
+      <c r="G294" s="13" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
@@ -9396,6 +9994,7 @@
         <v>142</v>
       </c>
       <c r="F295" s="7" t="n"/>
+      <c r="G295" s="13" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="7" t="inlineStr">
@@ -9418,6 +10017,7 @@
         <v>146</v>
       </c>
       <c r="F296" s="7" t="n"/>
+      <c r="G296" s="13" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
@@ -9440,6 +10040,7 @@
         <v>150</v>
       </c>
       <c r="F297" s="7" t="n"/>
+      <c r="G297" s="13" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="7" t="inlineStr">
@@ -9462,6 +10063,7 @@
         <v>128</v>
       </c>
       <c r="F298" s="7" t="n"/>
+      <c r="G298" s="13" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
@@ -9484,6 +10086,7 @@
         <v>137</v>
       </c>
       <c r="F299" s="7" t="n"/>
+      <c r="G299" s="13" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="7" t="inlineStr">
@@ -9506,6 +10109,7 @@
         <v>149</v>
       </c>
       <c r="F300" s="7" t="n"/>
+      <c r="G300" s="13" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
@@ -9528,6 +10132,7 @@
         <v>149</v>
       </c>
       <c r="F301" s="7" t="n"/>
+      <c r="G301" s="13" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
@@ -9550,6 +10155,7 @@
         <v>142</v>
       </c>
       <c r="F302" s="7" t="n"/>
+      <c r="G302" s="13" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
@@ -9572,6 +10178,7 @@
         <v>151</v>
       </c>
       <c r="F303" s="7" t="n"/>
+      <c r="G303" s="13" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="7" t="inlineStr">
@@ -9594,6 +10201,7 @@
         <v>137</v>
       </c>
       <c r="F304" s="7" t="n"/>
+      <c r="G304" s="13" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
@@ -9616,6 +10224,7 @@
         <v>139</v>
       </c>
       <c r="F305" s="7" t="n"/>
+      <c r="G305" s="13" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="7" t="inlineStr">
@@ -9638,6 +10247,7 @@
         <v>137</v>
       </c>
       <c r="F306" s="7" t="n"/>
+      <c r="G306" s="13" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
@@ -9660,6 +10270,7 @@
         <v>139</v>
       </c>
       <c r="F307" s="7" t="n"/>
+      <c r="G307" s="13" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="7" t="inlineStr">
@@ -9682,6 +10293,7 @@
         <v>145</v>
       </c>
       <c r="F308" s="7" t="n"/>
+      <c r="G308" s="13" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
@@ -9704,6 +10316,7 @@
         <v>141</v>
       </c>
       <c r="F309" s="7" t="n"/>
+      <c r="G309" s="13" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="7" t="inlineStr">
@@ -9726,6 +10339,7 @@
         <v>139</v>
       </c>
       <c r="F310" s="7" t="n"/>
+      <c r="G310" s="13" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
@@ -9748,6 +10362,7 @@
         <v>145</v>
       </c>
       <c r="F311" s="7" t="n"/>
+      <c r="G311" s="13" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
@@ -9770,6 +10385,7 @@
         <v>160.5</v>
       </c>
       <c r="F312" s="7" t="n"/>
+      <c r="G312" s="13" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
@@ -9792,6 +10408,7 @@
         <v>146</v>
       </c>
       <c r="F313" s="7" t="n"/>
+      <c r="G313" s="13" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
@@ -9814,6 +10431,7 @@
         <v>152.3</v>
       </c>
       <c r="F314" s="7" t="n"/>
+      <c r="G314" s="13" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
@@ -9836,6 +10454,7 @@
         <v>146</v>
       </c>
       <c r="F315" s="7" t="n"/>
+      <c r="G315" s="13" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="7" t="inlineStr">
@@ -9858,6 +10477,7 @@
         <v>145</v>
       </c>
       <c r="F316" s="7" t="n"/>
+      <c r="G316" s="13" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
@@ -9880,6 +10500,7 @@
         <v>143.5</v>
       </c>
       <c r="F317" s="7" t="n"/>
+      <c r="G317" s="13" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="7" t="inlineStr">
@@ -9902,6 +10523,7 @@
         <v>141.5</v>
       </c>
       <c r="F318" s="7" t="n"/>
+      <c r="G318" s="13" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
@@ -9924,6 +10546,7 @@
         <v>133.5</v>
       </c>
       <c r="F319" s="7" t="n"/>
+      <c r="G319" s="13" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
@@ -9946,6 +10569,7 @@
         <v>146</v>
       </c>
       <c r="F320" s="7" t="n"/>
+      <c r="G320" s="13" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
@@ -9968,6 +10592,7 @@
         <v>137</v>
       </c>
       <c r="F321" s="7" t="n"/>
+      <c r="G321" s="13" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="7" t="inlineStr">
@@ -9990,6 +10615,7 @@
         <v>142</v>
       </c>
       <c r="F322" s="7" t="n"/>
+      <c r="G322" s="13" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
@@ -10012,6 +10638,7 @@
         <v>145</v>
       </c>
       <c r="F323" s="7" t="n"/>
+      <c r="G323" s="13" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="7" t="inlineStr">
@@ -10034,6 +10661,7 @@
         <v>133</v>
       </c>
       <c r="F324" s="7" t="n"/>
+      <c r="G324" s="13" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
@@ -10056,6 +10684,7 @@
         <v>140</v>
       </c>
       <c r="F325" s="7" t="n"/>
+      <c r="G325" s="13" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="7" t="inlineStr">
@@ -10078,6 +10707,7 @@
         <v>143.4</v>
       </c>
       <c r="F326" s="7" t="n"/>
+      <c r="G326" s="13" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
@@ -10100,6 +10730,7 @@
         <v>154</v>
       </c>
       <c r="F327" s="7" t="n"/>
+      <c r="G327" s="13" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="7" t="inlineStr">
@@ -10122,6 +10753,7 @@
         <v>146</v>
       </c>
       <c r="F328" s="7" t="n"/>
+      <c r="G328" s="13" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
@@ -10144,6 +10776,7 @@
         <v>145.5</v>
       </c>
       <c r="F329" s="7" t="n"/>
+      <c r="G329" s="13" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
@@ -10166,6 +10799,7 @@
         <v>143</v>
       </c>
       <c r="F330" s="7" t="n"/>
+      <c r="G330" s="13" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
@@ -10188,6 +10822,7 @@
         <v>146.5</v>
       </c>
       <c r="F331" s="7" t="n"/>
+      <c r="G331" s="13" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
@@ -10210,6 +10845,7 @@
         <v>152</v>
       </c>
       <c r="F332" s="7" t="n"/>
+      <c r="G332" s="13" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
@@ -10232,6 +10868,7 @@
         <v>128.5</v>
       </c>
       <c r="F333" s="7" t="n"/>
+      <c r="G333" s="13" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
@@ -10254,6 +10891,7 @@
         <v>138.5</v>
       </c>
       <c r="F334" s="7" t="n"/>
+      <c r="G334" s="13" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
@@ -10276,6 +10914,7 @@
         <v>149</v>
       </c>
       <c r="F335" s="7" t="n"/>
+      <c r="G335" s="13" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
@@ -10298,6 +10937,7 @@
         <v>144</v>
       </c>
       <c r="F336" s="7" t="n"/>
+      <c r="G336" s="13" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
@@ -10320,6 +10960,7 @@
         <v>153</v>
       </c>
       <c r="F337" s="7" t="n"/>
+      <c r="G337" s="13" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
@@ -10342,6 +10983,7 @@
         <v>137.5</v>
       </c>
       <c r="F338" s="7" t="n"/>
+      <c r="G338" s="13" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
@@ -10364,6 +11006,7 @@
         <v>139</v>
       </c>
       <c r="F339" s="7" t="n"/>
+      <c r="G339" s="13" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
@@ -10386,6 +11029,7 @@
         <v>141</v>
       </c>
       <c r="F340" s="7" t="n"/>
+      <c r="G340" s="13" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
@@ -10408,6 +11052,7 @@
         <v>146.5</v>
       </c>
       <c r="F341" s="7" t="n"/>
+      <c r="G341" s="13" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
@@ -10434,6 +11079,7 @@
           <t>Revisar talla: +5 cm en tres meses y medio (141 cm en junio)</t>
         </is>
       </c>
+      <c r="G342" s="13" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
@@ -10456,6 +11102,7 @@
         <v>140</v>
       </c>
       <c r="F343" s="7" t="n"/>
+      <c r="G343" s="13" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
@@ -10478,6 +11125,7 @@
         <v>126</v>
       </c>
       <c r="F344" s="7" t="n"/>
+      <c r="G344" s="13" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
@@ -10500,6 +11148,9 @@
         <v>162.5</v>
       </c>
       <c r="F345" s="7" t="n"/>
+      <c r="G345" s="13" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
@@ -10522,6 +11173,9 @@
         <v>155</v>
       </c>
       <c r="F346" s="7" t="n"/>
+      <c r="G346" s="13" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
@@ -10544,6 +11198,9 @@
         <v>154</v>
       </c>
       <c r="F347" s="7" t="n"/>
+      <c r="G347" s="13" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
@@ -10566,6 +11223,9 @@
         <v>143</v>
       </c>
       <c r="F348" s="7" t="n"/>
+      <c r="G348" s="13" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
@@ -10588,6 +11248,9 @@
         <v>150</v>
       </c>
       <c r="F349" s="7" t="n"/>
+      <c r="G349" s="13" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
@@ -10610,6 +11273,9 @@
         <v>163</v>
       </c>
       <c r="F350" s="7" t="n"/>
+      <c r="G350" s="13" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
@@ -10632,6 +11298,9 @@
         <v>172</v>
       </c>
       <c r="F351" s="7" t="n"/>
+      <c r="G351" s="13" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
@@ -10654,6 +11323,9 @@
         <v>148</v>
       </c>
       <c r="F352" s="7" t="n"/>
+      <c r="G352" s="13" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
@@ -10676,6 +11348,9 @@
         <v>158.5</v>
       </c>
       <c r="F353" s="7" t="n"/>
+      <c r="G353" s="13" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
@@ -10698,6 +11373,9 @@
         <v>156.5</v>
       </c>
       <c r="F354" s="7" t="n"/>
+      <c r="G354" s="13" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
@@ -10720,6 +11398,9 @@
         <v>161</v>
       </c>
       <c r="F355" s="7" t="n"/>
+      <c r="G355" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
@@ -10742,6 +11423,9 @@
         <v>154</v>
       </c>
       <c r="F356" s="7" t="n"/>
+      <c r="G356" s="13" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
@@ -10764,6 +11448,9 @@
         <v>161</v>
       </c>
       <c r="F357" s="7" t="n"/>
+      <c r="G357" s="13" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
@@ -10786,6 +11473,9 @@
         <v>154</v>
       </c>
       <c r="F358" s="7" t="n"/>
+      <c r="G358" s="13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
@@ -10808,6 +11498,9 @@
         <v>174</v>
       </c>
       <c r="F359" s="7" t="n"/>
+      <c r="G359" s="13" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
@@ -10834,6 +11527,9 @@
           <t>Figuraba como "Valentin Peretti" en febrero y junio; misma línea de talla y peso</t>
         </is>
       </c>
+      <c r="G360" s="13" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
@@ -10856,6 +11552,9 @@
         <v>167</v>
       </c>
       <c r="F361" s="7" t="n"/>
+      <c r="G361" s="13" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
@@ -10878,6 +11577,9 @@
         <v>158</v>
       </c>
       <c r="F362" s="7" t="n"/>
+      <c r="G362" s="13" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
@@ -10900,6 +11602,9 @@
         <v>174</v>
       </c>
       <c r="F363" s="7" t="n"/>
+      <c r="G363" s="13" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
@@ -10922,6 +11627,9 @@
         <v>146</v>
       </c>
       <c r="F364" s="7" t="n"/>
+      <c r="G364" s="13" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
@@ -10944,6 +11652,9 @@
         <v>162</v>
       </c>
       <c r="F365" s="7" t="n"/>
+      <c r="G365" s="13" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
@@ -10966,6 +11677,9 @@
         <v>149</v>
       </c>
       <c r="F366" s="7" t="n"/>
+      <c r="G366" s="13" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
@@ -10988,6 +11702,9 @@
         <v>147.5</v>
       </c>
       <c r="F367" s="7" t="n"/>
+      <c r="G367" s="13" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
@@ -11010,6 +11727,9 @@
         <v>170</v>
       </c>
       <c r="F368" s="7" t="n"/>
+      <c r="G368" s="13" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
@@ -11032,6 +11752,9 @@
         <v>162.5</v>
       </c>
       <c r="F369" s="7" t="n"/>
+      <c r="G369" s="13" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
@@ -11054,6 +11777,9 @@
         <v>167</v>
       </c>
       <c r="F370" s="7" t="n"/>
+      <c r="G370" s="13" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
@@ -11076,6 +11802,9 @@
         <v>146.5</v>
       </c>
       <c r="F371" s="7" t="n"/>
+      <c r="G371" s="13" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
@@ -11098,6 +11827,9 @@
         <v>167</v>
       </c>
       <c r="F372" s="7" t="n"/>
+      <c r="G372" s="13" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
@@ -11120,6 +11852,9 @@
         <v>170</v>
       </c>
       <c r="F373" s="7" t="n"/>
+      <c r="G373" s="13" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
@@ -11142,6 +11877,9 @@
         <v>167</v>
       </c>
       <c r="F374" s="7" t="n"/>
+      <c r="G374" s="13" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
@@ -11164,6 +11902,9 @@
         <v>173.3</v>
       </c>
       <c r="F375" s="7" t="n"/>
+      <c r="G375" s="13" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
@@ -11190,6 +11931,9 @@
           <t>Revisar talla: +5 cm entre junio (172) y octubre (177)</t>
         </is>
       </c>
+      <c r="G376" s="13" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
@@ -11212,6 +11956,9 @@
         <v>156</v>
       </c>
       <c r="F377" s="7" t="n"/>
+      <c r="G377" s="13" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
@@ -11234,6 +11981,9 @@
         <v>155.5</v>
       </c>
       <c r="F378" s="7" t="n"/>
+      <c r="G378" s="13" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
@@ -11256,6 +12006,9 @@
         <v>177</v>
       </c>
       <c r="F379" s="7" t="n"/>
+      <c r="G379" s="13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
@@ -11282,6 +12035,9 @@
           <t>Apellido figuraba como "´Perilli"</t>
         </is>
       </c>
+      <c r="G380" s="13" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
@@ -11304,6 +12060,9 @@
         <v>170</v>
       </c>
       <c r="F381" s="7" t="n"/>
+      <c r="G381" s="13" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
@@ -11326,6 +12085,9 @@
         <v>163.5</v>
       </c>
       <c r="F382" s="7" t="n"/>
+      <c r="G382" s="13" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
@@ -11348,6 +12110,85 @@
         <v>176</v>
       </c>
       <c r="F383" s="7" t="n"/>
+      <c r="G383" s="13" t="n">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Óptimo hasta (mm)</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Aceptable hasta (mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Cómo se lee: hasta el primer valor es zona óptima; hasta el segundo, aceptable; por encima, exceso. Ej. 2013: ≤49 óptimo, 50–69 aceptable, ≥70 exceso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Si una categoría no figura acá, el portal muestra los pliegues sin clasificar por zona.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
